--- a/Documentacion/ApiBEducativo.xlsx
+++ b/Documentacion/ApiBEducativo.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\iGeo SONDEF\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\iGeo SONDEF\Documents\Visual Studio 2022\Projects\ApiBEducativo\Documentacion\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="92">
   <si>
     <t>Cliente</t>
   </si>
@@ -47,9 +47,6 @@
     <t>VANCUVER</t>
   </si>
   <si>
-    <t>ModUsuario</t>
-  </si>
-  <si>
     <t>Email</t>
   </si>
   <si>
@@ -128,9 +125,6 @@
     <t>RegistroUsuarioDispositivo</t>
   </si>
   <si>
-    <t>ModPagos</t>
-  </si>
-  <si>
     <t>Oid</t>
   </si>
   <si>
@@ -143,9 +137,6 @@
     <t>DiasAtraso</t>
   </si>
   <si>
-    <t>ModCalificaciones</t>
-  </si>
-  <si>
     <t>Materia</t>
   </si>
   <si>
@@ -167,12 +158,6 @@
     <t>Matricula</t>
   </si>
   <si>
-    <t>ModAlumno</t>
-  </si>
-  <si>
-    <t>Foto</t>
-  </si>
-  <si>
     <t>HoraSalida</t>
   </si>
   <si>
@@ -260,9 +245,6 @@
     <t>UsuarioEntregaObs</t>
   </si>
   <si>
-    <t>ModEstatusCarrousel</t>
-  </si>
-  <si>
     <t>Descripcion</t>
   </si>
   <si>
@@ -281,39 +263,6 @@
     <t>xpNivel</t>
   </si>
   <si>
-    <t>ModModulos</t>
-  </si>
-  <si>
-    <t>Modulos</t>
-  </si>
-  <si>
-    <t>RutaImagen</t>
-  </si>
-  <si>
-    <t>/img/menus/pago.png</t>
-  </si>
-  <si>
-    <t>Pagos</t>
-  </si>
-  <si>
-    <t>ModuloId</t>
-  </si>
-  <si>
-    <t>ModuloDesc</t>
-  </si>
-  <si>
-    <t>ModuloPerfil</t>
-  </si>
-  <si>
-    <t>ModModuloPerfil</t>
-  </si>
-  <si>
-    <t>ModRegistroUsuarioDispositivo</t>
-  </si>
-  <si>
-    <t>ModCliente</t>
-  </si>
-  <si>
     <t>Clase Modelo</t>
   </si>
   <si>
@@ -321,6 +270,36 @@
   </si>
   <si>
     <t>Clase Beducativo Xpo</t>
+  </si>
+  <si>
+    <t>ClienteDTO</t>
+  </si>
+  <si>
+    <t>RegistroUsuarioDispositivoDTO</t>
+  </si>
+  <si>
+    <t>UsuarioDTO</t>
+  </si>
+  <si>
+    <t>AlumnoDTO</t>
+  </si>
+  <si>
+    <t>PagosDTO</t>
+  </si>
+  <si>
+    <t>CalificacionesDTO</t>
+  </si>
+  <si>
+    <t>EstatusCarrouselDTO</t>
+  </si>
+  <si>
+    <t>AlumnoInscritoId</t>
+  </si>
+  <si>
+    <t>UrlFoto</t>
+  </si>
+  <si>
+    <t>PagoCubierto</t>
   </si>
 </sst>
 </file>
@@ -660,7 +639,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M69"/>
+  <dimension ref="A1:M57"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="20.5546875" bestFit="1" customWidth="1"/>
@@ -681,10 +660,10 @@
         <v>0</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="K1" s="4" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
@@ -698,7 +677,7 @@
         <v>3</v>
       </c>
       <c r="D2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F2" t="s">
         <v>1</v>
@@ -710,10 +689,10 @@
         <v>3</v>
       </c>
       <c r="I2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
@@ -730,7 +709,7 @@
         <v>1</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
@@ -763,10 +742,10 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
@@ -774,19 +753,19 @@
         <v>1</v>
       </c>
       <c r="B8" t="s">
+        <v>28</v>
+      </c>
+      <c r="C8" t="s">
         <v>29</v>
       </c>
-      <c r="C8" t="s">
-        <v>30</v>
-      </c>
       <c r="F8" t="s">
         <v>1</v>
       </c>
       <c r="G8" t="s">
+        <v>28</v>
+      </c>
+      <c r="H8" t="s">
         <v>29</v>
-      </c>
-      <c r="H8" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
@@ -797,7 +776,7 @@
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
@@ -808,12 +787,12 @@
         <v>1</v>
       </c>
       <c r="C10" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
-        <v>7</v>
+        <v>84</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
@@ -821,433 +800,349 @@
         <v>1</v>
       </c>
       <c r="B15" t="s">
+        <v>7</v>
+      </c>
+      <c r="C15" t="s">
         <v>8</v>
       </c>
-      <c r="C15" t="s">
+      <c r="D15" t="s">
         <v>9</v>
       </c>
-      <c r="D15" t="s">
+      <c r="E15" t="s">
         <v>10</v>
       </c>
-      <c r="E15" t="s">
+      <c r="F15" t="s">
         <v>11</v>
       </c>
-      <c r="F15" t="s">
+      <c r="G15" t="s">
         <v>12</v>
       </c>
-      <c r="G15" t="s">
+      <c r="H15" t="s">
         <v>13</v>
       </c>
-      <c r="H15" t="s">
+      <c r="I15" t="s">
         <v>14</v>
       </c>
-      <c r="I15" t="s">
+      <c r="J15" t="s">
         <v>15</v>
       </c>
-      <c r="J15" t="s">
+      <c r="K15" t="s">
         <v>16</v>
-      </c>
-      <c r="K15" t="s">
-        <v>17</v>
       </c>
       <c r="L15" t="s">
         <v>3</v>
       </c>
       <c r="M15" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16" t="s">
+        <v>17</v>
+      </c>
+      <c r="C16" t="s">
+        <v>18</v>
+      </c>
+      <c r="D16" t="s">
+        <v>19</v>
+      </c>
+      <c r="E16" t="s">
+        <v>20</v>
+      </c>
+      <c r="F16" t="s">
+        <v>21</v>
+      </c>
+      <c r="G16" t="s">
+        <v>22</v>
+      </c>
+      <c r="H16" t="s">
+        <v>23</v>
+      </c>
+      <c r="I16" t="s">
+        <v>24</v>
+      </c>
+      <c r="J16" t="s">
+        <v>25</v>
+      </c>
+      <c r="K16" t="s">
+        <v>26</v>
+      </c>
+      <c r="L16" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A21" t="s">
+        <v>1</v>
+      </c>
+      <c r="B21" t="s">
+        <v>89</v>
+      </c>
+      <c r="C21" t="s">
+        <v>9</v>
+      </c>
+      <c r="D21" t="s">
+        <v>40</v>
+      </c>
+      <c r="E21" t="s">
+        <v>41</v>
+      </c>
+      <c r="F21" t="s">
+        <v>42</v>
+      </c>
+      <c r="G21" t="s">
+        <v>43</v>
+      </c>
+      <c r="H21" t="s">
+        <v>90</v>
+      </c>
+      <c r="I21" t="s">
+        <v>44</v>
+      </c>
+      <c r="J21" t="s">
+        <v>45</v>
+      </c>
+      <c r="K21" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A25" s="3" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>1</v>
+      </c>
+      <c r="B26" t="s">
+        <v>34</v>
+      </c>
+      <c r="C26" t="s">
         <v>35</v>
       </c>
-      <c r="B16" t="s">
-        <v>18</v>
-      </c>
-      <c r="C16" t="s">
-        <v>19</v>
-      </c>
-      <c r="D16" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" t="s">
-        <v>21</v>
-      </c>
-      <c r="F16" t="s">
-        <v>22</v>
-      </c>
-      <c r="G16" t="s">
-        <v>23</v>
-      </c>
-      <c r="H16" t="s">
-        <v>24</v>
-      </c>
-      <c r="I16" t="s">
-        <v>25</v>
-      </c>
-      <c r="J16" t="s">
-        <v>26</v>
-      </c>
-      <c r="K16" t="s">
-        <v>27</v>
-      </c>
-      <c r="L16" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="2" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" t="s">
-        <v>1</v>
-      </c>
-      <c r="B19" t="s">
-        <v>79</v>
-      </c>
-      <c r="C19" t="s">
+      <c r="D26" t="s">
+        <v>91</v>
+      </c>
+      <c r="E26" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A27" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A30" s="3" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20">
-        <v>1</v>
-      </c>
-      <c r="B20" t="s">
-        <v>89</v>
-      </c>
-      <c r="C20" t="s">
+    <row r="31" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
+        <v>1</v>
+      </c>
+      <c r="B31" t="s">
+        <v>37</v>
+      </c>
+      <c r="C31" t="s">
+        <v>38</v>
+      </c>
+      <c r="D31" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A34" s="3" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
+        <v>1</v>
+      </c>
+      <c r="B35" t="s">
+        <v>64</v>
+      </c>
+      <c r="C35" t="s">
+        <v>60</v>
+      </c>
+      <c r="D35" t="s">
+        <v>61</v>
+      </c>
+      <c r="E35" t="s">
+        <v>62</v>
+      </c>
+      <c r="F35" t="s">
+        <v>58</v>
+      </c>
+      <c r="G35" t="s">
+        <v>66</v>
+      </c>
+      <c r="H35" t="s">
+        <v>67</v>
+      </c>
+      <c r="I35" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A38" s="4" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A39" t="s">
+        <v>48</v>
+      </c>
+      <c r="B39" t="s">
+        <v>49</v>
+      </c>
+      <c r="C39" t="s">
+        <v>56</v>
+      </c>
+      <c r="D39" t="s">
+        <v>50</v>
+      </c>
+      <c r="E39" t="s">
+        <v>70</v>
+      </c>
+      <c r="F39" t="s">
+        <v>65</v>
+      </c>
+      <c r="G39" t="s">
+        <v>69</v>
+      </c>
+      <c r="H39" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A40">
+        <v>1</v>
+      </c>
+      <c r="B40" t="s">
+        <v>57</v>
+      </c>
+      <c r="C40">
+        <v>3</v>
+      </c>
+      <c r="D40" s="1">
+        <v>45924</v>
+      </c>
+      <c r="F40">
+        <v>1</v>
+      </c>
+      <c r="G40" s="1">
+        <v>45924.333333333336</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A41">
+        <v>2</v>
+      </c>
+      <c r="B41" t="s">
+        <v>59</v>
+      </c>
+      <c r="C41">
+        <v>1</v>
+      </c>
+      <c r="D41" s="1">
+        <v>45924</v>
+      </c>
+      <c r="F41">
+        <v>1</v>
+      </c>
+      <c r="G41" s="1">
+        <v>45924.333333333336</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A43" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A44" t="s">
+        <v>48</v>
+      </c>
+      <c r="B44" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A45">
+        <v>1</v>
+      </c>
+      <c r="B45" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A46">
+        <v>2</v>
+      </c>
+      <c r="B46" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A47">
+        <v>3</v>
+      </c>
+      <c r="B47" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A48">
+        <v>4</v>
+      </c>
+      <c r="B48" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A51" s="3" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="3" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" t="s">
-        <v>1</v>
-      </c>
-      <c r="B23" t="s">
-        <v>90</v>
-      </c>
-      <c r="C23" t="s">
-        <v>91</v>
-      </c>
-      <c r="D23" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="3" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
-        <v>1</v>
-      </c>
-      <c r="B26" t="s">
-        <v>90</v>
-      </c>
-      <c r="C26" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="3" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
-        <v>1</v>
-      </c>
-      <c r="B29" t="s">
-        <v>90</v>
-      </c>
-      <c r="C29" t="s">
-        <v>91</v>
-      </c>
-      <c r="D29" t="s">
-        <v>87</v>
-      </c>
-      <c r="E29" t="s">
-        <v>11</v>
-      </c>
-      <c r="F29" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
-        <v>1</v>
-      </c>
-      <c r="B33" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" t="s">
-        <v>43</v>
-      </c>
-      <c r="D33" t="s">
-        <v>44</v>
-      </c>
-      <c r="E33" t="s">
-        <v>45</v>
-      </c>
-      <c r="F33" t="s">
-        <v>46</v>
-      </c>
-      <c r="G33" t="s">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A52" t="s">
+        <v>1</v>
+      </c>
+      <c r="B52" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A56" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A57" t="s">
         <v>48</v>
       </c>
-      <c r="H33" t="s">
-        <v>49</v>
-      </c>
-      <c r="I33" t="s">
-        <v>50</v>
-      </c>
-      <c r="J33" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A37" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A38" t="s">
-        <v>1</v>
-      </c>
-      <c r="B38" t="s">
-        <v>36</v>
-      </c>
-      <c r="C38" t="s">
-        <v>37</v>
-      </c>
-      <c r="D38" t="s">
-        <v>13</v>
-      </c>
-      <c r="E38" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A39" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A42" s="3" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A43" t="s">
-        <v>1</v>
-      </c>
-      <c r="B43" t="s">
-        <v>40</v>
-      </c>
-      <c r="C43" t="s">
-        <v>41</v>
-      </c>
-      <c r="D43" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A46" s="3" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A47" t="s">
-        <v>1</v>
-      </c>
-      <c r="B47" t="s">
-        <v>69</v>
-      </c>
-      <c r="C47" t="s">
-        <v>65</v>
-      </c>
-      <c r="D47" t="s">
-        <v>66</v>
-      </c>
-      <c r="E47" t="s">
-        <v>67</v>
-      </c>
-      <c r="F47" t="s">
-        <v>63</v>
-      </c>
-      <c r="G47" t="s">
-        <v>71</v>
-      </c>
-      <c r="H47" t="s">
-        <v>72</v>
-      </c>
-      <c r="I47" t="s">
+      <c r="B57" t="s">
+        <v>75</v>
+      </c>
+      <c r="C57" t="s">
+        <v>76</v>
+      </c>
+      <c r="D57" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A50" s="4" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A51" t="s">
-        <v>53</v>
-      </c>
-      <c r="B51" t="s">
-        <v>54</v>
-      </c>
-      <c r="C51" t="s">
-        <v>61</v>
-      </c>
-      <c r="D51" t="s">
-        <v>55</v>
-      </c>
-      <c r="E51" t="s">
-        <v>75</v>
-      </c>
-      <c r="F51" t="s">
-        <v>70</v>
-      </c>
-      <c r="G51" t="s">
-        <v>74</v>
-      </c>
-      <c r="H51" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A52">
-        <v>1</v>
-      </c>
-      <c r="B52" t="s">
-        <v>62</v>
-      </c>
-      <c r="C52">
-        <v>3</v>
-      </c>
-      <c r="D52" s="1">
-        <v>45924</v>
-      </c>
-      <c r="F52">
-        <v>1</v>
-      </c>
-      <c r="G52" s="1">
-        <v>45924.333333333336</v>
-      </c>
-    </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A53">
-        <v>2</v>
-      </c>
-      <c r="B53" t="s">
-        <v>64</v>
-      </c>
-      <c r="C53">
-        <v>1</v>
-      </c>
-      <c r="D53" s="1">
-        <v>45924</v>
-      </c>
-      <c r="F53">
-        <v>1</v>
-      </c>
-      <c r="G53" s="1">
-        <v>45924.333333333336</v>
-      </c>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A55" s="4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A56" t="s">
-        <v>53</v>
-      </c>
-      <c r="B56" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A57">
-        <v>1</v>
-      </c>
-      <c r="B57" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A58">
-        <v>2</v>
-      </c>
-      <c r="B58" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A59">
-        <v>3</v>
-      </c>
-      <c r="B59" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A60">
-        <v>4</v>
-      </c>
-      <c r="B60" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A63" s="3" t="s">
+      <c r="E57" t="s">
         <v>78</v>
-      </c>
-    </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A64" t="s">
-        <v>1</v>
-      </c>
-      <c r="B64" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A68" s="4" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A69" t="s">
-        <v>53</v>
-      </c>
-      <c r="B69" t="s">
-        <v>81</v>
-      </c>
-      <c r="C69" t="s">
-        <v>82</v>
-      </c>
-      <c r="D69" t="s">
-        <v>83</v>
-      </c>
-      <c r="E69" t="s">
-        <v>84</v>
       </c>
     </row>
   </sheetData>
